--- a/docs/03_test/部署登録画面テスト.xlsx
+++ b/docs/03_test/部署登録画面テスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B722E73F-19C5-4BC4-B567-E8264F784CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FE66FC-6E55-4543-B7EB-1F01AC263752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
   <sheets>
     <sheet name="部署登録テスト" sheetId="1" r:id="rId1"/>
@@ -514,18 +514,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -539,41 +551,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,15 +591,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>257163</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1378101</xdr:colOff>
+      <xdr:colOff>1464285</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>190580</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -628,14 +622,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1949450" y="2527300"/>
-          <a:ext cx="2933851" cy="1549480"/>
+          <a:off x="2193913" y="2362200"/>
+          <a:ext cx="2775572" cy="1714500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,31 +1517,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="17" t="s">
@@ -1558,260 +1551,254 @@
       <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="11"/>
+      <c r="B32" s="13"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="10"/>
+      <c r="B34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>1</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>2</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="5">
         <v>99</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>3</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="5">
         <v>1000</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>4</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>5</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="5">
         <v>110</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>6</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="5">
         <v>110</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>7</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="5">
         <v>110</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>8</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="5">
         <v>101</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>9</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="5">
         <v>110</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>10</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="5">
         <v>999</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="14"/>
+      <c r="B45" s="4"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
@@ -1865,12 +1852,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A8:D8"/>
@@ -1880,6 +1861,12 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
